--- a/data/trans_orig/P37C3_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P37C3_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la creencia de que las vacunas son efectivas en 2023</t>
+          <t>Población según la creencia de que las vacunas son efectivas en 2023 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>729</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9349</t>
+          <t>9979</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4610</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10888</t>
+          <t>10449</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15499</t>
+          <t>15626</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>698</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>8097</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18653</t>
+          <t>18015</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10372</t>
+          <t>10599</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25616</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16486</t>
+          <t>17887</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18479</t>
+          <t>18167</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37497</t>
+          <t>36613</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77930</t>
+          <t>78163</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115081</t>
+          <t>114981</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59145</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84945</t>
+          <t>85157</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>142661</t>
+          <t>145374</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>188258</t>
+          <t>190530</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>361949</t>
+          <t>361354</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>402349</t>
+          <t>400319</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>345647</t>
+          <t>346100</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>374486</t>
+          <t>375508</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>720718</t>
+          <t>718080</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>769413</t>
+          <t>767259</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,7%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9278</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12978</t>
+          <t>11468</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7492</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2218</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>10822</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>11292</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27557</t>
+          <t>28111</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10478</t>
+          <t>10455</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26311</t>
+          <t>28102</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24883</t>
+          <t>23590</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47524</t>
+          <t>47365</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67944</t>
+          <t>68034</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101518</t>
+          <t>101485</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66642</t>
+          <t>66379</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92767</t>
+          <t>91937</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>143578</t>
+          <t>142919</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>185028</t>
+          <t>183942</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>324895</t>
+          <t>325160</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>361160</t>
+          <t>362602</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>264774</t>
+          <t>266893</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>294743</t>
+          <t>295496</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>599440</t>
+          <t>601091</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>647492</t>
+          <t>646179</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,79%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7154</t>
+          <t>7346</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>595</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10722</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13650</t>
+          <t>13820</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14681</t>
+          <t>14959</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>10937</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>56474</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16149</t>
+          <t>15430</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16954</t>
+          <t>17623</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>63199</t>
+          <t>65110</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32877</t>
+          <t>35421</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>157004</t>
+          <t>158869</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27578</t>
+          <t>27131</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43106</t>
+          <t>43957</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49701</t>
+          <t>50765</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>191203</t>
+          <t>195101</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>441863</t>
+          <t>442177</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>619290</t>
+          <t>614035</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109431</t>
+          <t>109414</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>128008</t>
+          <t>127896</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>564103</t>
+          <t>561992</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>755345</t>
+          <t>755204</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,95%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>561</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10048</t>
+          <t>10528</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12008</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>17217</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7861</t>
+          <t>8597</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>22096</t>
+          <t>21484</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34806</t>
+          <t>33989</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>62552</t>
+          <t>62455</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>10942</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>32489</t>
+          <t>33840</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>47701</t>
+          <t>48795</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>89625</t>
+          <t>89101</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>216331</t>
+          <t>210431</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>278037</t>
+          <t>274105</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>67957</t>
+          <t>77414</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>200849</t>
+          <t>203323</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>282003</t>
+          <t>290359</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>463518</t>
+          <t>461718</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>694747</t>
+          <t>692456</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>757665</t>
+          <t>758145</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>733455</t>
+          <t>732290</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>892560</t>
+          <t>878907</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1440257</t>
+          <t>1443107</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1655461</t>
+          <t>1642915</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,09%</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>174</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>7236</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2462</t>
+          <t>2918</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12361</t>
+          <t>12641</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12712</t>
+          <t>11834</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19789</t>
+          <t>20654</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>23283</t>
+          <t>23244</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>45962</t>
+          <t>46484</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>27688</t>
+          <t>28047</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>58525</t>
+          <t>58910</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>56275</t>
+          <t>55796</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>95653</t>
+          <t>96557</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>98694</t>
+          <t>95343</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>136376</t>
+          <t>137919</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>110855</t>
+          <t>114438</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>176693</t>
+          <t>176519</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>219936</t>
+          <t>218261</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>299252</t>
+          <t>299185</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>292630</t>
+          <t>290891</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>333925</t>
+          <t>334105</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>603138</t>
+          <t>604739</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>687671</t>
+          <t>684198</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>908934</t>
+          <t>909420</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1009066</t>
+          <t>1009343</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,41%</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9631</t>
+          <t>10148</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>527</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>11319</t>
+          <t>11619</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>602</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>895</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7340</t>
+          <t>6689</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>32845</t>
+          <t>35651</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>23903</t>
+          <t>23926</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>52118</t>
+          <t>50056</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>33574</t>
+          <t>35018</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>71984</t>
+          <t>72371</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>45908</t>
+          <t>47294</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>91888</t>
+          <t>89494</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>149693</t>
+          <t>151543</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>193240</t>
+          <t>193965</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>209112</t>
+          <t>212792</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>271082</t>
+          <t>276801</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>124674</t>
+          <t>125330</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>173590</t>
+          <t>171659</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>519436</t>
+          <t>521101</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>566010</t>
+          <t>566302</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>657865</t>
+          <t>652138</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>724633</t>
+          <t>722626</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,11%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>19403</t>
+          <t>20811</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>19758</t>
+          <t>20428</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>12577</t>
+          <t>12922</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>32843</t>
+          <t>33290</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>21494</t>
+          <t>21463</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>44728</t>
+          <t>46250</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>12662</t>
+          <t>12853</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>26518</t>
+          <t>27516</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>38296</t>
+          <t>38876</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>66260</t>
+          <t>66578</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>124250</t>
+          <t>124137</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>194416</t>
+          <t>195140</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,47 +5063,47 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>5,82%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>131762</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>106500</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>159574</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
           <t>3,71%</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>131762</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>102614</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>157303</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>249453</t>
+          <t>247965</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>337997</t>
+          <t>338982</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>551219</t>
+          <t>533176</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>783650</t>
+          <t>780991</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>536440</t>
+          <t>543682</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>725680</t>
+          <t>725197</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1202553</t>
+          <t>1172364</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1482502</t>
+          <t>1462810</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2348292</t>
+          <t>2352818</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2645964</t>
+          <t>2690876</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2656091</t>
+          <t>2655854</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2896062</t>
+          <t>2877052</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>5036195</t>
+          <t>5047588</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5405392</t>
+          <t>5425228</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,56%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37C3_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P37C3_2023-Clase-trans_orig.xlsx
@@ -725,102 +725,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>671</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9979</t>
+          <t>9052</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3965</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>9974</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,14%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1236</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3716</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>4325</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1466</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>10449</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15626</t>
+          <t>15687</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,17 +873,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>8215</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>10268</t>
+          <t>11126</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>20345</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16408</t>
+          <t>17900</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10599</t>
+          <t>11596</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25322</t>
+          <t>27289</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9476</t>
+          <t>10863</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17887</t>
+          <t>18098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>25884</t>
+          <t>28763</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18167</t>
+          <t>19938</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36613</t>
+          <t>40339</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>94794</t>
+          <t>104425</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78163</t>
+          <t>85399</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>114981</t>
+          <t>122844</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>71331</t>
+          <t>79328</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59331</t>
+          <t>66377</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85157</t>
+          <t>94101</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>166125</t>
+          <t>183754</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>145374</t>
+          <t>159683</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>190530</t>
+          <t>206974</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>382424</t>
+          <t>416271</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>361354</t>
+          <t>396991</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>400319</t>
+          <t>437286</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>361784</t>
+          <t>392978</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>346100</t>
+          <t>378093</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>375508</t>
+          <t>407193</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>744207</t>
+          <t>809250</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>718080</t>
+          <t>781819</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>767259</t>
+          <t>833878</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,41%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>504040</t>
+          <t>549430</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>504040</t>
+          <t>549430</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>504040</t>
+          <t>549430</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>446770</t>
+          <t>487665</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>446770</t>
+          <t>487665</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>446770</t>
+          <t>487665</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>950810</t>
+          <t>1037095</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>950810</t>
+          <t>1037095</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>950810</t>
+          <t>1037095</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7549</t>
+          <t>6573</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10329</t>
+          <t>10115</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11468</t>
+          <t>11970</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>8755</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10822</t>
+          <t>11878</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17688</t>
+          <t>19515</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11292</t>
+          <t>11949</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28111</t>
+          <t>29921</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17026</t>
+          <t>20103</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10455</t>
+          <t>13256</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28102</t>
+          <t>31254</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>34714</t>
+          <t>39619</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23590</t>
+          <t>29486</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47365</t>
+          <t>53957</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -1746,102 +1746,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>84456</t>
+          <t>92571</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68034</t>
+          <t>75760</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101485</t>
+          <t>111877</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>23,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>87956</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>73812</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>102246</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>20,87%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>17,51%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>24,26%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>180527</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>157680</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>203575</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>20,03%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>17,49%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>22,58%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>78873</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>66379</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>91937</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>20,68%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>17,41%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>24,11%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>163329</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>142919</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>183942</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>19,66%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>17,2%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>343828</t>
+          <t>364245</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>325160</t>
+          <t>344899</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>362602</t>
+          <t>383084</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,67 +1894,67 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>280253</t>
+          <t>307608</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>266893</t>
+          <t>291248</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>295496</t>
+          <t>323962</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>76,87%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>789</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>671853</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>647274</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>698467</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>74,54%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>71,81%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>77,49%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>789</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>624081</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>601091</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>646179</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>75,13%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>72,36%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>77,79%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>449376</t>
+          <t>479923</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>449376</t>
+          <t>479923</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>449376</t>
+          <t>479923</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>381328</t>
+          <t>421468</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>381328</t>
+          <t>421468</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>381328</t>
+          <t>421468</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>830705</t>
+          <t>901391</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>830705</t>
+          <t>901391</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>830705</t>
+          <t>901391</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7346</t>
+          <t>5995</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>9734</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10808</t>
+          <t>12242</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>8732</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>17536</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>646</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6729</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14959</t>
+          <t>18688</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31371</t>
+          <t>33371</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>22569</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56474</t>
+          <t>47584</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8883</t>
+          <t>9357</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4806</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15430</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>40254</t>
+          <t>42728</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17623</t>
+          <t>31092</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>65110</t>
+          <t>57900</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>95455</t>
+          <t>107924</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35421</t>
+          <t>91396</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>158869</t>
+          <t>126633</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>35070</t>
+          <t>40169</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27131</t>
+          <t>31176</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43957</t>
+          <t>49659</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>130525</t>
+          <t>148093</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50765</t>
+          <t>128847</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>195101</t>
+          <t>169567</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>529903</t>
+          <t>315834</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>442177</t>
+          <t>293216</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>614035</t>
+          <t>335483</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>118938</t>
+          <t>133807</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109414</t>
+          <t>122652</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>127896</t>
+          <t>143188</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>648841</t>
+          <t>449641</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>561992</t>
+          <t>425660</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>755204</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>72,16%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>664648</t>
+          <t>467733</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>664648</t>
+          <t>467733</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>664648</t>
+          <t>467733</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>165730</t>
+          <t>186336</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>165730</t>
+          <t>186336</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>165730</t>
+          <t>186336</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>830378</t>
+          <t>654069</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>830378</t>
+          <t>654069</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>830378</t>
+          <t>654069</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>828</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10528</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10459</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -2884,67 +2884,67 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>9580</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17217</t>
+          <t>17733</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>4252</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>8334</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
           <t>0,5%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>3915</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>1396</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>8597</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>13495</t>
+          <t>14190</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21484</t>
+          <t>22764</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>47319</t>
+          <t>54235</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33989</t>
+          <t>39748</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>62455</t>
+          <t>71186</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>22572</t>
+          <t>26815</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10942</t>
+          <t>19150</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33840</t>
+          <t>37663</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>69891</t>
+          <t>81050</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>48795</t>
+          <t>65849</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>89101</t>
+          <t>107409</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>244651</t>
+          <t>275106</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>210431</t>
+          <t>246101</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>274105</t>
+          <t>310493</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>155164</t>
+          <t>171050</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>77414</t>
+          <t>152832</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>203323</t>
+          <t>190351</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>399816</t>
+          <t>446156</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>290359</t>
+          <t>410249</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>461718</t>
+          <t>482814</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>24,38%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>724911</t>
+          <t>783144</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>692456</t>
+          <t>748110</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>758145</t>
+          <t>816387</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>789223</t>
+          <t>651245</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>732290</t>
+          <t>630822</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>878907</t>
+          <t>672258</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1514135</t>
+          <t>1434389</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1443107</t>
+          <t>1389980</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1642915</t>
+          <t>1472825</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>74,37%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1027306</t>
+          <t>1123250</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1027306</t>
+          <t>1123250</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1027306</t>
+          <t>1123250</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>974079</t>
+          <t>857073</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>974079</t>
+          <t>857073</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>974079</t>
+          <t>857073</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2001386</t>
+          <t>1980324</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2001386</t>
+          <t>1980324</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2001386</t>
+          <t>1980324</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>7611</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>929</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2238</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>434</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7236</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12641</t>
+          <t>16480</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>12059</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>14270</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>8321</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20654</t>
+          <t>23087</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>33040</t>
+          <t>48156</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>23244</t>
+          <t>35119</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>46484</t>
+          <t>65718</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>40067</t>
+          <t>40213</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>28047</t>
+          <t>31122</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>58910</t>
+          <t>51464</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>73107</t>
+          <t>88368</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>55796</t>
+          <t>71879</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>96557</t>
+          <t>106892</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>116560</t>
+          <t>135587</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>95343</t>
+          <t>114512</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>137919</t>
+          <t>158006</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>149726</t>
+          <t>171792</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>114438</t>
+          <t>153628</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>176519</t>
+          <t>190867</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>266286</t>
+          <t>307379</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>218261</t>
+          <t>280169</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>299185</t>
+          <t>335628</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>313089</t>
+          <t>364083</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>290891</t>
+          <t>338956</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>334105</t>
+          <t>387426</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>636948</t>
+          <t>605099</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>604739</t>
+          <t>582356</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>684198</t>
+          <t>625368</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>950038</t>
+          <t>969182</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>909420</t>
+          <t>936963</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1009343</t>
+          <t>1001814</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>72,53%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>470452</t>
+          <t>557065</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>470452</t>
+          <t>557065</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>470452</t>
+          <t>557065</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>833398</t>
+          <t>824246</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>833398</t>
+          <t>824246</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>833398</t>
+          <t>824246</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1303850</t>
+          <t>1381311</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1303850</t>
+          <t>1381311</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1303850</t>
+          <t>1381311</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>7190</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,22 +4205,22 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>541</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>11619</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>711</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4258,12 +4258,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,17 +4283,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,17 +4318,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6689</t>
+          <t>7802</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>15631</t>
+          <t>18357</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>35651</t>
+          <t>38184</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>33738</t>
+          <t>37248</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>23926</t>
+          <t>26776</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>50056</t>
+          <t>54605</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>49369</t>
+          <t>55605</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>35018</t>
+          <t>40135</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>72371</t>
+          <t>82440</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>67337</t>
+          <t>71401</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>47294</t>
+          <t>50204</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>89494</t>
+          <t>93273</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>171979</t>
+          <t>192188</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>151543</t>
+          <t>170898</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>193965</t>
+          <t>214928</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>239316</t>
+          <t>263590</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>212792</t>
+          <t>232734</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>276801</t>
+          <t>299455</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,01%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>149732</t>
+          <t>139930</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>125330</t>
+          <t>115758</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>171659</t>
+          <t>163251</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>543854</t>
+          <t>603901</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>521101</t>
+          <t>578762</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>566302</t>
+          <t>626700</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>693585</t>
+          <t>743831</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>652138</t>
+          <t>704915</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>722626</t>
+          <t>777214</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>72,7%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>235338</t>
+          <t>231881</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>235338</t>
+          <t>231881</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>235338</t>
+          <t>231881</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>753081</t>
+          <t>837141</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>753081</t>
+          <t>837141</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>753081</t>
+          <t>837141</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>988419</t>
+          <t>1069022</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>988419</t>
+          <t>1069022</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>988419</t>
+          <t>1069022</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,67 +4817,67 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>20811</t>
+          <t>19982</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>11321</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>5937</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>21243</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>10255</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>4803</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>20428</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,17 +4887,17 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>21101</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>12922</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>33290</t>
+          <t>31796</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -4930,102 +4930,102 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>32160</t>
+          <t>37446</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>21463</t>
+          <t>26050</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>50465</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>20888</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>14646</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>30247</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>58334</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>45158</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>73448</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>19227</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>12853</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>27516</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>51387</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>38876</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>66578</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>161457</t>
+          <t>191533</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>124137</t>
+          <t>164287</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>195140</t>
+          <t>225367</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
+          <t>5,62%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
           <t>4,82%</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>131762</t>
+          <t>144599</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>106500</t>
+          <t>122406</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>159574</t>
+          <t>167912</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>293219</t>
+          <t>336133</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>247965</t>
+          <t>299323</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>338982</t>
+          <t>377944</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>703254</t>
+          <t>787015</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>533176</t>
+          <t>737173</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>780991</t>
+          <t>846109</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>662143</t>
+          <t>742483</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>543682</t>
+          <t>699779</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>725197</t>
+          <t>783098</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1365397</t>
+          <t>1529498</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1172364</t>
+          <t>1466015</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1462810</t>
+          <t>1602971</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>2443887</t>
+          <t>2383508</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2352818</t>
+          <t>2317024</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2690876</t>
+          <t>2436428</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2731000</t>
+          <t>2694638</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2655854</t>
+          <t>2650994</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2877052</t>
+          <t>2742698</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>5174887</t>
+          <t>5078146</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>5047588</t>
+          <t>4999667</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5425228</t>
+          <t>5149131</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>73,32%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3351161</t>
+          <t>3409283</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3351161</t>
+          <t>3409283</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3351161</t>
+          <t>3409283</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>3554387</t>
+          <t>3613929</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3554387</t>
+          <t>3613929</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3554387</t>
+          <t>3613929</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>6905547</t>
+          <t>7023212</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6905547</t>
+          <t>7023212</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6905547</t>
+          <t>7023212</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
